--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk10pct_wu200000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk10pct_wu200000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23847</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
